--- a/question_bank/MATHS KCNAG.xlsx
+++ b/question_bank/MATHS KCNAG.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7500" firstSheet="3" activeTab="5"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7500" firstSheet="4" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="Ex 1 Addition &amp; Substraction" sheetId="4" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <sheet name="Ex 38 Unitary Method" sheetId="3" r:id="rId4"/>
     <sheet name="Ex 39 Unitary Method" sheetId="1" r:id="rId5"/>
     <sheet name="Ex 40 Unitary M Time &amp; Distance" sheetId="2" r:id="rId6"/>
+    <sheet name="Ex 7-14 Units" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -29,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="219">
   <si>
     <t>1. 5 men can do piece of work in 21 days. In how many days will 7 men do the same work?</t>
   </si>
@@ -497,13 +498,263 @@
   </si>
   <si>
     <t>26. 9/10 of a property cost ₹6543, find the cost of 3/8 of it.</t>
+  </si>
+  <si>
+    <t>21. The total weight of 4 boys of your class is 212 Kg. The weight of 3 of them are 49 Kg 700 gm and 54 Kg 600 gm. Find the weight of the fourth boy.</t>
+  </si>
+  <si>
+    <t>ex10)1. Add the following quantities : 18 yrs. 4 wks. 20 days + 15 yrs. 2 wks. 16 days + 14 yrs. 3 wks. 12 days.</t>
+  </si>
+  <si>
+    <t>ex10)2. Add the following quantities : 12 yrs. 10 months 26 days + 10 yrs. 9 months 28 days + 28 yrs. 11 months 30 days.</t>
+  </si>
+  <si>
+    <t>ex10)4. Add the following quantities : 80 yds. 1 ft. 10 inches + 273 yds. 2 ft. 11 ins. + 789 yds. 1 ft. 9 ins. + 856 yds. 1 ft. 6 ins. + 714 yds. 2 ft. 4 ins.</t>
+  </si>
+  <si>
+    <t>ex10)5. Add the following quantities : 8 miles 170 yds. 2ft. 9 ins. + 21 miles 30 yds. 1. ft. 3 ins. + 775 miles 210 yds. 1 ft. 6 ins. + 825 miles 90 yds. 2 ft. 7 ins + 999 miles 810 yds. 4 ins.</t>
+  </si>
+  <si>
+    <t>ex10)6. Add the following quantities : 1760 miles 124 yds. 10 ins. + 7160 miles 444 yds. 9 ins. + 6017 miles 888 yds. 3 ins. + 601 miles 666 yds. 6 ins. + 8243 miles 222 yds. 4 ins.</t>
+  </si>
+  <si>
+    <t>ex10)7. Add the following quantities : 118 yrs. 9 weeks 4 days + 215 yrs. 11 wks. 6 days + 820 yrs. 10 wks. 6 days + 916 yrs. 8 wks. 5 days.</t>
+  </si>
+  <si>
+    <t>ex10)8. Add the following quantities : 17 yrs. 112 days + 173 yrs. 214 days + 891 yrs. 316 days + 1976 yrs. 218 days + 984 yrs. 19 days.</t>
+  </si>
+  <si>
+    <t>ex10)9. Add the following quantities : 12 days 12 hrs. 12 mins 12 secs + 24 days 15 hrs. 58 mins. 48 secs. + 36 days 20 hrs. 23 mins. 30 secs. + 66 days 18 hrs. 17 mins. 20 secs. + 20 days 19 hrs. 14 mins. 10 secs.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ex11)4. 1787 miles 112 yds. 1 ft. 10 ins. - 787 miles 217 yds. 1 ft. 11 ins. </t>
+  </si>
+  <si>
+    <t>ex11)5. 1270 yds. 1 ft. 3 ins. - 897 yds. 2 ft. 4 ins.</t>
+  </si>
+  <si>
+    <t>ex11)6. (a) 17 miles 1720 yds. 2 ft. 4 ins. - 1721 yds. 2 ft. 6 ins.</t>
+  </si>
+  <si>
+    <t>ex11)6. (b) 4 days 3 minutes - 2 days 20 hours 15 minutes. [R.K.M. (N)2002]</t>
+  </si>
+  <si>
+    <t>ex11)8. 20 days 18 hrs. 19 mins. 31 secs. - 12 days 19 hrs. 44 mins. 40 secs.</t>
+  </si>
+  <si>
+    <t>ex11)7. 11 months 10 days 6 hrs. 17 mins. 47 secs. - 9 months 20 days 21 hrs. 37 mins. 32 secs.</t>
+  </si>
+  <si>
+    <t>ex11)9. 78 yrs. 8 months 20 days 30 mins. - 29yrs. 9months 21 days 40 mins. 37 secs.</t>
+  </si>
+  <si>
+    <t>ex11)11. What is to be subtracted from 20 miles to get 7 miles 18 yds. 3 inches?</t>
+  </si>
+  <si>
+    <t>ex11)13. When Jadu was 7 years 9 months 21 days old, his sister was born. When Jadu will be 31 yrs. 6 months 9 days old, what will then be his sister's age?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ex11)14. In a race starting from the same place one man ran up to a distance of 17310 feet while another man ran 4 miles 170 yds. Who won and by how much distance? </t>
+  </si>
+  <si>
+    <t>ex12)2. Find the product:  212 yds. 2 ft. 9 inches x 35;</t>
+  </si>
+  <si>
+    <t>ex12)3. Find the product: 16 miles 66 yds. 6 inches x 36;</t>
+  </si>
+  <si>
+    <t>ex12)5. Find the product: 7 months 9 days 20 mins. × 168.</t>
+  </si>
+  <si>
+    <t>ex12)9. The length of a lawn is 22 yds. 1 ft. 9 inches and breadth is 10 yds. 2 ft. 6 inches. How much distance is covered by walking 120 times along its four sides?</t>
+  </si>
+  <si>
+    <t>ex13)1. Divide: b. 1 mile 1265 yds. by 10, 15, 25 and 30; c. 66 yrs. 8 months by 12, 16, 24 and 30;</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">ex13)2. Divide: 10 days 1 hr. 38 mins. 24 secs. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>÷</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 5 hrs. 2 mins. 3 secs.</t>
+    </r>
+  </si>
+  <si>
+    <t>ex13)3. Divide: 25 days 10 hrs. 1 min. 15 secs.  ÷ 5 days 2 hrs. 15 secs.</t>
+  </si>
+  <si>
+    <t>ex13)4. Divide: (i) 15 miles  ÷ 12 feet 6 inches; (ii) 88 miles  ÷ 352 yds.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">ex13)5. Divide: (a) 2 months 4 days 2 hrs 27 mins. 36 secs. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>÷</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 5 days 8 hrs. 12 mins. 18 secs. (b) 17 yds. 2 ft. 8ins.  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">÷ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2 yds. 1 ft. 8 ins.</t>
+    </r>
+  </si>
+  <si>
+    <t>ex14)41. The cost of a watch is ₹40.72 find the cost of 16 watches.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ex14)42. If the price of 5 Kg. of sugar be ₹ 93-85 find the price of 14 Kg. sugar.</t>
+  </si>
+  <si>
+    <t>ex14)43. I have ₹375.08. If I buy a dozen of pens at 28-04 each, how much shall I have left?</t>
+  </si>
+  <si>
+    <t>ex14)44. The price of a book is ₹12.25. How many books can be had for ₹294?</t>
+  </si>
+  <si>
+    <t>ex14)45. After purchasing 15 pieces of cloth at ₹81.50 each and 12 wrappers at the rate of ₹57.20. each, I found that I had with me ₹72.50 only. How much did I have at first?</t>
+  </si>
+  <si>
+    <t>ex14)46. How many cards each costing 15p. can be had for ₹3.75?</t>
+  </si>
+  <si>
+    <t>ex14)47. Ram and Hari together have ₹12.45; Hari and Jadu ₹11.40 and Jadu and Ram ₹13.35. Find how much each has?</t>
+  </si>
+  <si>
+    <t>ex14)48. ₹10.80 was divided among 45 children such that each boy got 22p. and each girl 28p. How many boys and girls were there?</t>
+  </si>
+  <si>
+    <t>ex14)49. The price of a Shirt is ₹103.20 and that of a cloth ₹71.20. How many shirts and cloths in equal in number can be had for ₹5232.00?</t>
+  </si>
+  <si>
+    <t>ex14)50. I give away ₹30 to a number of beggars giving ₹1.50 to each. Find out the total number of beggars.</t>
+  </si>
+  <si>
+    <t>ex14)51. In a picnic we have allotted ₹270 for buying soft drinks. How many bottles of soft drink can be purchased at a price of ₹9 each?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ex7)13. 16 equal balls weigh 6 Kg. 5 Hg. 1 Dg. 2 g. 8 dg., find the weight of one ball. </t>
+  </si>
+  <si>
+    <t>ex7)14. Find the circumference of a wheel that makes 1130 revolutions to go 2 Km. 33 Dm. 91dm.</t>
+  </si>
+  <si>
+    <t>ex7)15. Among how many persons 3 Quintals 72 Kg. 6 Hg. wheat will be distributed, so that each gets 4 Kg. 6 Hg.?</t>
+  </si>
+  <si>
+    <t>ex7)16. A rope is divided into seven equal parts. The length of each part is 5 m. 67 cm. If it is divided into 9 equal parts, what will be the length of each part?</t>
+  </si>
+  <si>
+    <t>ex7)17. Along a path of 735 metres long there are 35 trees planted at equal gaps. What is the distance between two trees?</t>
+  </si>
+  <si>
+    <t>ex7)18. Find the cost of 10 Myriagram at 35 paise per gram.</t>
+  </si>
+  <si>
+    <t>ex7)19. A litre of water weights 1 Kilogram. If a man carries 2 buckets, each containing 21-5 litres of water, What weight of water does he carry?</t>
+  </si>
+  <si>
+    <t>ex7)20. The production of rice in a factory was 1859127 Kg. Express these in metric tonnes, quintals, myriagram and Kg.</t>
+  </si>
+  <si>
+    <t>ex7)22. Rohan needs 12 Dg 5 g of meat per day to feed his pet dog. Find the cost of meat at 400 per Kg that he needs to buy in the month of August.</t>
+  </si>
+  <si>
+    <t>ex7)23. The circumference of a wheel is 9 m 75 dm and it turns 4 times per second. Find the time taken by the wheel to cover 390 Km.</t>
+  </si>
+  <si>
+    <t>ex8)20. How many weeks make 3 yrs. 32 days?</t>
+  </si>
+  <si>
+    <t>ex8)21. 2nd January 1970 was Monday. What day was 21" April of that year?</t>
+  </si>
+  <si>
+    <t>ex8)23. What day was 30th August 1954?</t>
+  </si>
+  <si>
+    <t>ex8)22. 1 January 1952 was Friday. What day was 1st January 1953?</t>
+  </si>
+  <si>
+    <t>ex8)24. What day was 13th February 1953?</t>
+  </si>
+  <si>
+    <t>ex8)25. What day was 8th October 1950?</t>
+  </si>
+  <si>
+    <t>ex8)26. What days was 28th December 2003?</t>
+  </si>
+  <si>
+    <t>ex8)27. A school was closed on 11th May and opened on 1 July during summer season. For how many days the school was closed? How many Saturdays were there during the vacation if the closing day was Friday?</t>
+  </si>
+  <si>
+    <t>ex9) Reduce to miles, yards, feet and inches : 1. 87521 inches. 2. 70895 ft. 3. 67890 yds. 4. 60006060 inches.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ex9)5. A hill is 8976703 inches high. Reduce its height to miles, yds., feet and inches. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ex9) Reduce to years, months, days hours and minutes etc. 6. 70800 secs. 7. 91627 mins. 8. 21809 hrs. 9. 26789days. 10. 6178 months. </t>
+  </si>
+  <si>
+    <t>ex9)11. 72080 days how many years?</t>
+  </si>
+  <si>
+    <t>ex9)12. Reduce 29050 farthings to pounds, shillings etc.</t>
+  </si>
+  <si>
+    <t>ex9)13. Calculate the number of days from 20th January to 7th May in the year 1916.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -524,6 +775,12 @@
       <color rgb="FF000000"/>
       <name val="Google Sans Text"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -539,7 +796,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -547,11 +804,20 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -568,6 +834,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1662,7 +1931,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" ht="30">
       <c r="A5" s="2" t="s">
         <v>140</v>
       </c>
@@ -1923,7 +2192,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="42.75">
+    <row r="3" spans="1:2" ht="28.5">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -1931,7 +2200,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="42.75">
+    <row r="4" spans="1:2" ht="28.5">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -1939,7 +2208,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="42.75">
+    <row r="5" spans="1:2" ht="28.5">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
@@ -1955,7 +2224,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="42.75">
+    <row r="7" spans="1:2" ht="28.5">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
@@ -1987,7 +2256,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="57">
+    <row r="11" spans="1:2" ht="42.75">
       <c r="A11" s="1" t="s">
         <v>9</v>
       </c>
@@ -1995,7 +2264,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="42.75">
+    <row r="12" spans="1:2" ht="28.5">
       <c r="A12" s="1" t="s">
         <v>10</v>
       </c>
@@ -2003,7 +2272,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="114">
+    <row r="13" spans="1:2" ht="85.5">
       <c r="A13" s="1" t="s">
         <v>11</v>
       </c>
@@ -2011,7 +2280,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="57">
+    <row r="14" spans="1:2" ht="42.75">
       <c r="A14" s="1" t="s">
         <v>12</v>
       </c>
@@ -2160,7 +2429,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:2" ht="30">
       <c r="A17" s="2" t="s">
         <v>134</v>
       </c>
@@ -2171,4 +2440,538 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B65"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="63" style="2" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" s="6" customFormat="1">
+      <c r="A1" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="30">
+      <c r="A2" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="B2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="30">
+      <c r="A3" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="B3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="30">
+      <c r="A4" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="B4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="45">
+      <c r="A5" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="B5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="30">
+      <c r="A6" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="B6" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="B7" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="45">
+      <c r="A8" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="B8" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="30">
+      <c r="A9" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="B9" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="45">
+      <c r="A10" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="B10" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="45">
+      <c r="A11" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="B11" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="45.75" thickBot="1">
+      <c r="A12" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="B12" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="B13" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="30">
+      <c r="A14" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="B14" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="B15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="B16" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="B17" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="B18" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="B19" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="60.75" thickBot="1">
+      <c r="A20" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="B20" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="30">
+      <c r="A21" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="B21" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="30">
+      <c r="A22" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="B22" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ht="30">
+      <c r="A23" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="B23" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="B24" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="B25" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" ht="30.75" thickBot="1">
+      <c r="A26" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="B26" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" ht="30">
+      <c r="A27" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="B27" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" ht="30">
+      <c r="A28" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="B28" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" ht="45">
+      <c r="A29" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="B29" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" ht="45">
+      <c r="A30" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="B30" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" ht="45">
+      <c r="A31" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="B31" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" ht="30">
+      <c r="A32" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="B32" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" ht="30">
+      <c r="A33" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="B33" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" ht="45.75" thickBot="1">
+      <c r="A34" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="B34" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" ht="30">
+      <c r="A35" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="B35" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="B36" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="B37" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38" s="2">
+        <v>11</v>
+      </c>
+      <c r="B38" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" ht="30">
+      <c r="A39" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="B39" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" ht="30">
+      <c r="A40" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="B40" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" ht="30">
+      <c r="A41" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="B41" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" ht="30">
+      <c r="A42" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="B42" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" ht="30">
+      <c r="A43" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="B43" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" ht="45">
+      <c r="A44" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="B44" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" ht="45.75" thickBot="1">
+      <c r="A45" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="B45" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="B46" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="B47" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="B48" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" ht="45.75" thickBot="1">
+      <c r="A49" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="B49" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" ht="30">
+      <c r="A50" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="B50" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="B51" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
+      <c r="A52" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B52" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="A53" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B53" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" ht="30.75" thickBot="1">
+      <c r="A54" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="B54" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
+      <c r="A55" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="B55" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" ht="30">
+      <c r="A56" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B56" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" ht="30">
+      <c r="A57" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="B57" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" ht="30">
+      <c r="A58" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="B58" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" ht="45">
+      <c r="A59" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="B59" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
+      <c r="A60" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="B60" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" ht="30">
+      <c r="A61" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="B61" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" ht="30">
+      <c r="A62" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="B62" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" ht="45">
+      <c r="A63" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="B63" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" ht="30">
+      <c r="A64" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="B64" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" ht="45">
+      <c r="A65" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="B65" t="s">
+        <v>61</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/question_bank/MATHS KCNAG.xlsx
+++ b/question_bank/MATHS KCNAG.xlsx
@@ -9,16 +9,16 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7500" firstSheet="4" activeTab="6"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7500" firstSheet="2" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Ex 1 Addition &amp; Substraction" sheetId="4" r:id="rId1"/>
     <sheet name="Ex 2 Multiplication &amp; Division" sheetId="5" r:id="rId2"/>
     <sheet name="Ex 6 Misc Prob 1st Four Rules" sheetId="6" r:id="rId3"/>
-    <sheet name="Ex 38 Unitary Method" sheetId="3" r:id="rId4"/>
-    <sheet name="Ex 39 Unitary Method" sheetId="1" r:id="rId5"/>
-    <sheet name="Ex 40 Unitary M Time &amp; Distance" sheetId="2" r:id="rId6"/>
-    <sheet name="Ex 7-14 Units" sheetId="7" r:id="rId7"/>
+    <sheet name="Ex 7-14 Units" sheetId="7" r:id="rId4"/>
+    <sheet name="Ex 38 Unitary Method" sheetId="3" r:id="rId5"/>
+    <sheet name="Ex 39 Unitary Method" sheetId="1" r:id="rId6"/>
+    <sheet name="Ex 40 Unitary M Time &amp; Distance" sheetId="2" r:id="rId7"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -1893,6 +1893,540 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B65"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="63" style="2" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" s="6" customFormat="1">
+      <c r="A1" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="30">
+      <c r="A2" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="B2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="30">
+      <c r="A3" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="B3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="30">
+      <c r="A4" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="B4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="45">
+      <c r="A5" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="B5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="30">
+      <c r="A6" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="B6" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="B7" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="45">
+      <c r="A8" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="B8" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="30">
+      <c r="A9" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="B9" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="45">
+      <c r="A10" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="B10" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="45">
+      <c r="A11" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="B11" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="45.75" thickBot="1">
+      <c r="A12" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="B12" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="B13" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="30">
+      <c r="A14" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="B14" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="B15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="B16" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="B17" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="B18" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="B19" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="60.75" thickBot="1">
+      <c r="A20" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="B20" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="30">
+      <c r="A21" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="B21" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="30">
+      <c r="A22" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="B22" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ht="30">
+      <c r="A23" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="B23" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="B24" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="B25" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" ht="30.75" thickBot="1">
+      <c r="A26" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="B26" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" ht="30">
+      <c r="A27" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="B27" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" ht="30">
+      <c r="A28" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="B28" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" ht="45">
+      <c r="A29" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="B29" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" ht="45">
+      <c r="A30" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="B30" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" ht="45">
+      <c r="A31" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="B31" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" ht="30">
+      <c r="A32" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="B32" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" ht="30">
+      <c r="A33" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="B33" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" ht="45.75" thickBot="1">
+      <c r="A34" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="B34" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" ht="30">
+      <c r="A35" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="B35" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="B36" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="B37" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38" s="2">
+        <v>11</v>
+      </c>
+      <c r="B38" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" ht="30">
+      <c r="A39" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="B39" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" ht="30">
+      <c r="A40" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="B40" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" ht="30">
+      <c r="A41" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="B41" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" ht="30">
+      <c r="A42" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="B42" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" ht="30">
+      <c r="A43" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="B43" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" ht="45">
+      <c r="A44" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="B44" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" ht="45.75" thickBot="1">
+      <c r="A45" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="B45" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="B46" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="B47" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="B48" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" ht="45.75" thickBot="1">
+      <c r="A49" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="B49" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" ht="30">
+      <c r="A50" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="B50" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="B51" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
+      <c r="A52" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B52" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="A53" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B53" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" ht="30.75" thickBot="1">
+      <c r="A54" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="B54" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
+      <c r="A55" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="B55" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" ht="30">
+      <c r="A56" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B56" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" ht="30">
+      <c r="A57" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="B57" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" ht="30">
+      <c r="A58" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="B58" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" ht="45">
+      <c r="A59" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="B59" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
+      <c r="A60" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="B60" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" ht="30">
+      <c r="A61" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="B61" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" ht="30">
+      <c r="A62" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="B62" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" ht="45">
+      <c r="A63" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="B63" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" ht="30">
+      <c r="A64" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="B64" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" ht="45">
+      <c r="A65" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="B65" t="s">
+        <v>61</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B33"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -2168,7 +2702,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B14"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2293,7 +2827,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B17"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2440,538 +2974,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B65"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="63" style="2" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" s="6" customFormat="1">
-      <c r="A1" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="30">
-      <c r="A2" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="B2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="30">
-      <c r="A3" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="B3" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="30">
-      <c r="A4" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="B4" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="45">
-      <c r="A5" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="B5" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="30">
-      <c r="A6" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="B6" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
-      <c r="A7" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="B7" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="45">
-      <c r="A8" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="B8" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="30">
-      <c r="A9" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="B9" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="45">
-      <c r="A10" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="B10" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="45">
-      <c r="A11" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="B11" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="45.75" thickBot="1">
-      <c r="A12" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="B12" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2">
-      <c r="A13" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="B13" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" ht="30">
-      <c r="A14" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="B14" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2">
-      <c r="A15" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="B15" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2">
-      <c r="A16" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="B16" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2">
-      <c r="A17" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="B17" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2">
-      <c r="A18" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="B18" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2">
-      <c r="A19" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="B19" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" ht="60.75" thickBot="1">
-      <c r="A20" s="7" t="s">
-        <v>212</v>
-      </c>
-      <c r="B20" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" ht="30">
-      <c r="A21" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="B21" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" ht="30">
-      <c r="A22" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="B22" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" ht="30">
-      <c r="A23" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="B23" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2">
-      <c r="A24" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="B24" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2">
-      <c r="A25" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="B25" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" ht="30.75" thickBot="1">
-      <c r="A26" s="7" t="s">
-        <v>218</v>
-      </c>
-      <c r="B26" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" ht="30">
-      <c r="A27" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="B27" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" ht="30">
-      <c r="A28" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="B28" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" ht="45">
-      <c r="A29" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="B29" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" ht="45">
-      <c r="A30" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="B30" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" ht="45">
-      <c r="A31" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="B31" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" ht="30">
-      <c r="A32" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="B32" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" ht="30">
-      <c r="A33" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="B33" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" ht="45.75" thickBot="1">
-      <c r="A34" s="7" t="s">
-        <v>164</v>
-      </c>
-      <c r="B34" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" ht="30">
-      <c r="A35" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="B35" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2">
-      <c r="A36" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="B36" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2">
-      <c r="A37" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="B37" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2">
-      <c r="A38" s="2">
-        <v>11</v>
-      </c>
-      <c r="B38" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" ht="30">
-      <c r="A39" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="B39" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" ht="30">
-      <c r="A40" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="B40" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" ht="30">
-      <c r="A41" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="B41" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" ht="30">
-      <c r="A42" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="B42" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" ht="30">
-      <c r="A43" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="B43" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" ht="45">
-      <c r="A44" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="B44" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" ht="45.75" thickBot="1">
-      <c r="A45" s="7" t="s">
-        <v>174</v>
-      </c>
-      <c r="B45" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2">
-      <c r="A46" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="B46" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2">
-      <c r="A47" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="B47" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2">
-      <c r="A48" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="B48" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" ht="45.75" thickBot="1">
-      <c r="A49" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="B49" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" ht="30">
-      <c r="A50" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="B50" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2">
-      <c r="A51" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="B51" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2">
-      <c r="A52" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="B52" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2">
-      <c r="A53" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="B53" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" ht="30.75" thickBot="1">
-      <c r="A54" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="B54" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2">
-      <c r="A55" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="B55" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" ht="30">
-      <c r="A56" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="B56" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" ht="30">
-      <c r="A57" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="B57" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" ht="30">
-      <c r="A58" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="B58" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" ht="45">
-      <c r="A59" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="B59" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2">
-      <c r="A60" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="B60" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2" ht="30">
-      <c r="A61" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="B61" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" ht="30">
-      <c r="A62" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="B62" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2" ht="45">
-      <c r="A63" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="B63" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2" ht="30">
-      <c r="A64" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="B64" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2" ht="45">
-      <c r="A65" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="B65" t="s">
-        <v>61</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
 </file>